--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -36,102 +36,102 @@
     <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
+    <t xml:space="preserve">Galvarino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholchol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loncoche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teodoro Schmidt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacautín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarrica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pucón</t>
   </si>
   <si>
-    <t xml:space="preserve">Renaico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villarrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galvarino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholchol</t>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traiguén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
   </si>
   <si>
     <t xml:space="preserve">Saavedra</t>
   </si>
   <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cunco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacautín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loncoche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teodoro Schmidt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
-    <t xml:space="preserve">Purén</t>
+    <t xml:space="preserve">Victoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collipulli</t>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorbea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
     <t xml:space="preserve">Los Sauces</t>
   </si>
   <si>
-    <t xml:space="preserve">Gorbea</t>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
     <t xml:space="preserve">Temuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Traiguén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ercilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,13 +571,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9115</v>
+        <v>9106</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.95</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.77</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="4">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9120</v>
+        <v>9121</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10.14</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="5">
@@ -622,13 +622,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9106</v>
+        <v>9119</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.45</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9119</v>
+        <v>9109</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.81</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9121</v>
+        <v>9117</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8.06</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9116</v>
+        <v>9203</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7.17</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6.99</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="10">
@@ -707,13 +707,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9103</v>
+        <v>9120</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.34</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="11">
@@ -724,13 +724,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9114</v>
+        <v>9115</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6.26</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="12">
@@ -741,13 +741,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9203</v>
+        <v>9114</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.95</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="13">
@@ -758,13 +758,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9109</v>
+        <v>9103</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.55</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="14">
@@ -775,13 +775,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9205</v>
+        <v>9113</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5.29</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9113</v>
+        <v>9208</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.88</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9117</v>
+        <v>9118</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.55</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="17">
@@ -826,13 +826,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9104</v>
+        <v>9105</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.19</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="18">
@@ -843,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9208</v>
+        <v>9210</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19">
@@ -860,13 +860,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9108</v>
+        <v>9205</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2.98</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="21">
@@ -894,13 +894,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9105</v>
+        <v>9116</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="22">
@@ -911,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9118</v>
+        <v>9104</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9202</v>
+        <v>9211</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9206</v>
+        <v>9202</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="25">
@@ -962,13 +962,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9107</v>
+        <v>9108</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="26">
@@ -979,13 +979,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9101</v>
+        <v>9102</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="27">
@@ -996,13 +996,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>9210</v>
+        <v>9107</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="28">
@@ -1013,13 +1013,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9102</v>
+        <v>9112</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="30">
@@ -1047,13 +1047,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9112</v>
+        <v>9206</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.37</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="31">
@@ -1064,13 +1064,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>9211</v>
+        <v>9201</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.32</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="33">
@@ -1098,13 +1098,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>9201</v>
+        <v>9101</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-1.2</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.37</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6.42</v>
+        <v>64.21</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.01</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.74</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.48</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.99</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.97</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.91</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.79</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.63</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.16</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.11</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.08</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="15">
@@ -798,7 +798,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.88</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.85</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.79</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.27</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2.22</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.15</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.08</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2.07</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="23">
@@ -934,7 +934,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2.06</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.44</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.41</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.39</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.25</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.97</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.82</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.73</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.34</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.07</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:28</t>
+    <t xml:space="preserve">2026-10-05 08:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
